--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Mensa scolastica.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Mensa scolastica.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="144">
   <si>
     <r>
       <t xml:space="preserve">
@@ -185,7 +185,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Scopri di più</t>
+    <t>Richiedi il servizio</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -542,7 +542,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> Se hai espresso la preferenza per il tempo pieno, l'iscrizione alla mensa è obbligatoria. 
+      <t xml:space="preserve"> Se hai espresso la preferenza per il tempo pieno, l'iscrizione alla mensa è obbligatoria.
 Per ulteriori informazioni sul servizio, diete speciali e costi, [visita questa pagina](URL).</t>
     </r>
   </si>
@@ -587,7 +587,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è stata accolta. 
+      <t xml:space="preserve"> è stata accolta.
 </t>
     </r>
     <r>
@@ -847,7 +847,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> 
+      <t xml:space="preserve">
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -1225,8 +1225,8 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è in scadenza. 
-Ricarica il tuo borsellino elettronico con l'importo dovuto entro la data di scadenza. 
+      <t xml:space="preserve"> è in scadenza.
+Ricarica il tuo borsellino elettronico con l'importo dovuto entro la data di scadenza.
 </t>
     </r>
     <r>
@@ -1372,7 +1372,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> utile ai fini delle detrazioni in sede di dichiarazione dei redditi. 
+      <t xml:space="preserve"> utile ai fini delle detrazioni in sede di dichiarazione dei redditi.
 </t>
     </r>
     <r>
@@ -1382,7 +1382,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -1390,8 +1390,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> Trovi l'attestazione emessa in allegato a questo messaggio.
-Per accedere al portale, [visita questo sito](URL).</t>
+      <t xml:space="preserve"> Trovi l'attestazione emessa in allegato a questo messaggio.</t>
     </r>
   </si>
   <si>
@@ -1414,10 +1413,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>Scopri tutte le agevolazioni</t>
+    <t>Scopri le agevolazioni disponibili</t>
   </si>
   <si>
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
+  </si>
+  <si>
+    <t>Accedi al portale</t>
   </si>
   <si>
     <r>
@@ -1437,7 +1439,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1547,14 +1549,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -2424,12 +2418,12 @@
         <v>111</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>65</v>
@@ -2479,7 +2473,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>111</v>
@@ -2524,112 +2518,112 @@
         <v>111</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="N9" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="N9" s="34" t="s">
-        <v>123</v>
-      </c>
       <c r="O9" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E10" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="34" t="s">
-        <v>130</v>
+      <c r="G10" s="34" t="s">
+        <v>133</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="H10" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="L10" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="O10" s="34" t="s">
-        <v>131</v>
-      </c>
       <c r="P10" s="34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>65</v>
@@ -2653,16 +2647,16 @@
         <v>65</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="K11" s="34" t="s">
         <v>65</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M11" s="34" t="s">
         <v>65</v>
